--- a/data/sales-08.xlsx
+++ b/data/sales-08.xlsx
@@ -201,7 +201,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="16.200000000000003" customWidth="1"/>
     <col min="3" max="3" width="16.200000000000003" customWidth="1"/>
     <col min="4" max="4" width="12.15" customWidth="1"/>
     <col min="5" max="5" width="41.85" customWidth="1"/>
@@ -1226,59 +1226,743 @@
       </c>
     </row>
     <row r="19">
-      <c t="inlineStr" r="A19" s="2">
+      <c t="inlineStr" r="A19">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="65">
+        <v>71001</v>
+      </c>
+      <c r="C19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D19" s="66">
+        <v>200.00</v>
+      </c>
+      <c r="E19" s="66">
+        <v>70801.00</v>
+      </c>
+      <c r="F19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G19" s="66">
+        <v>70801.00</v>
+      </c>
+      <c r="H19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K19" s="65">
+        <v>0</v>
+      </c>
+      <c r="L19" s="65">
+        <v>0</v>
+      </c>
+      <c r="M19" s="66">
+        <v>70801.00</v>
+      </c>
+      <c r="N19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O19" s="66">
+        <v>120.00</v>
+      </c>
+      <c r="P19" s="65">
+        <v>597</v>
+      </c>
+      <c t="inlineStr" r="Q19">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c t="inlineStr" r="A20">
+        <is>
+          <t xml:space="preserve">09/08/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="65">
+        <v>27616</v>
+      </c>
+      <c r="C20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D20" s="66">
+        <v>210.00</v>
+      </c>
+      <c r="E20" s="66">
+        <v>27406.00</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G20" s="66">
+        <v>27406.00</v>
+      </c>
+      <c r="H20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K20" s="65">
+        <v>0</v>
+      </c>
+      <c r="L20" s="65">
+        <v>0</v>
+      </c>
+      <c r="M20" s="66">
+        <v>27406.00</v>
+      </c>
+      <c r="N20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P20" s="65">
+        <v>132</v>
+      </c>
+      <c t="inlineStr" r="Q20">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c t="inlineStr" r="A21">
+        <is>
+          <t xml:space="preserve">10/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="65">
+        <v>71003</v>
+      </c>
+      <c r="C21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D21" s="66">
+        <v>300.00</v>
+      </c>
+      <c r="E21" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G21" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="H21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I21" s="65">
+        <v>0</v>
+      </c>
+      <c r="J21" s="65">
+        <v>0</v>
+      </c>
+      <c r="K21" s="65">
+        <v>0</v>
+      </c>
+      <c r="L21" s="65">
+        <v>0</v>
+      </c>
+      <c r="M21" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="N21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P21" s="65">
+        <v>602</v>
+      </c>
+      <c t="inlineStr" r="Q21">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c t="inlineStr" r="A22">
+        <is>
+          <t xml:space="preserve">10/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="65">
+        <v>19148</v>
+      </c>
+      <c r="C22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D22" s="66">
+        <v>222.50</v>
+      </c>
+      <c r="E22" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G22" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="H22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K22" s="65">
+        <v>0</v>
+      </c>
+      <c r="L22" s="65">
+        <v>0</v>
+      </c>
+      <c r="M22" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="N22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O22" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P22" s="65">
+        <v>103</v>
+      </c>
+      <c t="inlineStr" r="Q22">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c t="inlineStr" r="A23">
+        <is>
+          <t xml:space="preserve">11/08/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="65">
+        <v>72613</v>
+      </c>
+      <c r="C23" s="66">
+        <v>110.00</v>
+      </c>
+      <c r="D23" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E23" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="F23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G23" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="H23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I23" s="65">
+        <v>0</v>
+      </c>
+      <c r="J23" s="65">
+        <v>0</v>
+      </c>
+      <c r="K23" s="65">
+        <v>0</v>
+      </c>
+      <c r="L23" s="65">
+        <v>0</v>
+      </c>
+      <c r="M23" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="N23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P23" s="65">
+        <v>632</v>
+      </c>
+      <c t="inlineStr" r="Q23">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c t="inlineStr" r="A24">
+        <is>
+          <t xml:space="preserve">11/08/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="65">
+        <v>22269</v>
+      </c>
+      <c r="C24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D24" s="66">
+        <v>140.00</v>
+      </c>
+      <c r="E24" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="F24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G24" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="H24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K24" s="65">
+        <v>0</v>
+      </c>
+      <c r="L24" s="65">
+        <v>0</v>
+      </c>
+      <c r="M24" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="N24" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O24" s="66">
+        <v>166.00</v>
+      </c>
+      <c r="P24" s="65">
+        <v>109</v>
+      </c>
+      <c t="inlineStr" r="Q24">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c t="inlineStr" r="A25">
+        <is>
+          <t xml:space="preserve">12/08/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="65">
+        <v>67035</v>
+      </c>
+      <c r="C25" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="D25" s="65">
+        <v>0</v>
+      </c>
+      <c r="E25" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="F25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G25" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="H25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K25" s="65">
+        <v>0</v>
+      </c>
+      <c r="L25" s="65">
+        <v>0</v>
+      </c>
+      <c r="M25" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="N25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O25" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P25" s="65">
+        <v>568</v>
+      </c>
+      <c t="inlineStr" r="Q25">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c t="inlineStr" r="A26">
+        <is>
+          <t xml:space="preserve">12/08/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="65">
+        <v>23489</v>
+      </c>
+      <c r="C26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D26" s="66">
+        <v>260.00</v>
+      </c>
+      <c r="E26" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="F26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G26" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="H26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I26" s="65">
+        <v>0</v>
+      </c>
+      <c r="J26" s="65">
+        <v>0</v>
+      </c>
+      <c r="K26" s="65">
+        <v>0</v>
+      </c>
+      <c r="L26" s="65">
+        <v>0</v>
+      </c>
+      <c r="M26" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="N26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P26" s="65">
+        <v>111</v>
+      </c>
+      <c t="inlineStr" r="Q26">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c t="inlineStr" r="A27">
+        <is>
+          <t xml:space="preserve">13/08/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="65">
+        <v>68394</v>
+      </c>
+      <c r="C27" s="66">
+        <v>80.00</v>
+      </c>
+      <c r="D27" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E27" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="F27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G27" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="H27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K27" s="65">
+        <v>0</v>
+      </c>
+      <c r="L27" s="65">
+        <v>0</v>
+      </c>
+      <c r="M27" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="N27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O27" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P27" s="65">
+        <v>597</v>
+      </c>
+      <c t="inlineStr" r="Q27">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c t="inlineStr" r="A28">
+        <is>
+          <t xml:space="preserve">13/08/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="65">
+        <v>21290</v>
+      </c>
+      <c r="C28" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D28" s="66">
+        <v>90.00</v>
+      </c>
+      <c r="E28" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="F28" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G28" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="H28" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I28" s="65">
+        <v>0</v>
+      </c>
+      <c r="J28" s="65">
+        <v>0</v>
+      </c>
+      <c r="K28" s="65">
+        <v>0</v>
+      </c>
+      <c r="L28" s="65">
+        <v>0</v>
+      </c>
+      <c r="M28" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="N28" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O28" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P28" s="65">
+        <v>93</v>
+      </c>
+      <c t="inlineStr" r="Q28">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c t="inlineStr" r="A29">
+        <is>
+          <t xml:space="preserve">14/08/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="65">
+        <v>73510</v>
+      </c>
+      <c r="C29" s="66">
+        <v>80.00</v>
+      </c>
+      <c r="D29" s="66">
+        <v>800.00</v>
+      </c>
+      <c r="E29" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="F29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G29" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="H29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K29" s="65">
+        <v>0</v>
+      </c>
+      <c r="L29" s="65">
+        <v>0</v>
+      </c>
+      <c r="M29" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="N29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O29" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P29" s="65">
+        <v>570</v>
+      </c>
+      <c t="inlineStr" r="Q29">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c t="inlineStr" r="A30">
+        <is>
+          <t xml:space="preserve">14/08/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="65">
+        <v>17640</v>
+      </c>
+      <c r="C30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D30" s="66">
+        <v>187.50</v>
+      </c>
+      <c r="E30" s="66">
+        <v>17452.50</v>
+      </c>
+      <c r="F30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G30" s="66">
+        <v>17452.50</v>
+      </c>
+      <c r="H30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K30" s="65">
+        <v>0</v>
+      </c>
+      <c r="L30" s="65">
+        <v>0</v>
+      </c>
+      <c r="M30" s="66">
+        <v>17452.50</v>
+      </c>
+      <c r="N30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P30" s="65">
+        <v>93</v>
+      </c>
+      <c t="inlineStr" r="Q30">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c t="inlineStr" r="A31" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <v>740595.00</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1211.70</v>
-      </c>
-      <c r="D19" s="2">
-        <v>4029.50</v>
-      </c>
-      <c r="E19" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="G19" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="M19" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="N19" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="O19" s="2">
-        <v>1255.00</v>
-      </c>
-      <c r="P19" s="2">
-        <v>5448.00</v>
+      <c r="B31" s="2">
+        <v>1295603.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1491.70</v>
+      </c>
+      <c r="D31" s="2">
+        <v>6639.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="M31" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="O31" s="2">
+        <v>1541.00</v>
+      </c>
+      <c r="P31" s="2">
+        <v>9655.00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q18"/>
+  <autoFilter ref="A2:Q30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/data/sales-08.xlsx
+++ b/data/sales-08.xlsx
@@ -215,7 +215,7 @@
     <col min="13" max="13" width="54" customWidth="1"/>
     <col min="14" max="14" width="6" customWidth="1"/>
     <col min="15" max="15" width="10.8" customWidth="1"/>
-    <col min="16" max="16" width="10.8" customWidth="1"/>
+    <col min="16" max="16" width="12.15" customWidth="1"/>
     <col min="17" max="17" width="54" customWidth="1"/>
   </cols>
   <sheetData>
@@ -430,35 +430,35 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">02/08/2026</t>
+          <t xml:space="preserve">01/08/2026</t>
         </is>
       </c>
       <c r="B5" s="65">
-        <v>83188</v>
+        <v>4699</v>
       </c>
       <c r="C5" s="66">
-        <v>150.00</v>
+        <v>0.00</v>
       </c>
       <c r="D5" s="66">
-        <v>800.00</v>
+        <v>220.00</v>
       </c>
       <c r="E5" s="66">
-        <v>82238.00</v>
+        <v>4479.00</v>
       </c>
       <c r="F5" s="66">
         <v>0.00</v>
       </c>
       <c r="G5" s="66">
-        <v>82238.00</v>
+        <v>4479.00</v>
       </c>
       <c r="H5" s="66">
         <v>0.00</v>
       </c>
-      <c r="I5" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J5" s="66">
-        <v>0.00</v>
+      <c r="I5" s="65">
+        <v>0</v>
+      </c>
+      <c r="J5" s="65">
+        <v>0</v>
       </c>
       <c r="K5" s="65">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="66">
-        <v>82238.00</v>
+        <v>4479.00</v>
       </c>
       <c r="N5" s="66">
         <v>0.00</v>
@@ -476,11 +476,11 @@
         <v>0.00</v>
       </c>
       <c r="P5" s="65">
-        <v>699</v>
+        <v>19</v>
       </c>
       <c t="inlineStr" r="Q5">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
@@ -491,22 +491,22 @@
         </is>
       </c>
       <c r="B6" s="65">
-        <v>24904</v>
+        <v>83188</v>
       </c>
       <c r="C6" s="66">
-        <v>0.00</v>
+        <v>150.00</v>
       </c>
       <c r="D6" s="66">
-        <v>162.50</v>
+        <v>800.00</v>
       </c>
       <c r="E6" s="66">
-        <v>24741.50</v>
+        <v>82238.00</v>
       </c>
       <c r="F6" s="66">
         <v>0.00</v>
       </c>
       <c r="G6" s="66">
-        <v>24741.50</v>
+        <v>82238.00</v>
       </c>
       <c r="H6" s="66">
         <v>0.00</v>
@@ -524,55 +524,55 @@
         <v>0</v>
       </c>
       <c r="M6" s="66">
-        <v>24741.50</v>
+        <v>82238.00</v>
       </c>
       <c r="N6" s="66">
         <v>0.00</v>
       </c>
       <c r="O6" s="66">
-        <v>172.00</v>
+        <v>0.00</v>
       </c>
       <c r="P6" s="65">
-        <v>126</v>
+        <v>699</v>
       </c>
       <c t="inlineStr" r="Q6">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">03/08/2026</t>
+          <t xml:space="preserve">02/08/2026</t>
         </is>
       </c>
       <c r="B7" s="65">
-        <v>74872</v>
+        <v>4382</v>
       </c>
       <c r="C7" s="66">
-        <v>120.00</v>
+        <v>0.00</v>
       </c>
       <c r="D7" s="66">
-        <v>310.00</v>
+        <v>162.50</v>
       </c>
       <c r="E7" s="66">
-        <v>74442.00</v>
+        <v>4219.50</v>
       </c>
       <c r="F7" s="66">
         <v>0.00</v>
       </c>
       <c r="G7" s="66">
-        <v>74442.00</v>
+        <v>4219.50</v>
       </c>
       <c r="H7" s="66">
         <v>0.00</v>
       </c>
-      <c r="I7" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J7" s="66">
-        <v>0.00</v>
+      <c r="I7" s="65">
+        <v>0</v>
+      </c>
+      <c r="J7" s="65">
+        <v>0</v>
       </c>
       <c r="K7" s="65">
         <v>0</v>
@@ -581,46 +581,46 @@
         <v>0</v>
       </c>
       <c r="M7" s="66">
-        <v>74442.00</v>
+        <v>4219.50</v>
       </c>
       <c r="N7" s="66">
         <v>0.00</v>
       </c>
       <c r="O7" s="66">
-        <v>85.00</v>
+        <v>0.00</v>
       </c>
       <c r="P7" s="65">
-        <v>615</v>
+        <v>22</v>
       </c>
       <c t="inlineStr" r="Q7">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">03/08/2026</t>
+          <t xml:space="preserve">02/08/2026</t>
         </is>
       </c>
       <c r="B8" s="65">
-        <v>20445</v>
+        <v>24904</v>
       </c>
       <c r="C8" s="66">
         <v>0.00</v>
       </c>
       <c r="D8" s="66">
-        <v>412.00</v>
+        <v>162.50</v>
       </c>
       <c r="E8" s="66">
-        <v>20033.00</v>
+        <v>24741.50</v>
       </c>
       <c r="F8" s="66">
         <v>0.00</v>
       </c>
       <c r="G8" s="66">
-        <v>20033.00</v>
+        <v>24741.50</v>
       </c>
       <c r="H8" s="66">
         <v>0.00</v>
@@ -638,16 +638,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="66">
-        <v>20033.00</v>
+        <v>24741.50</v>
       </c>
       <c r="N8" s="66">
         <v>0.00</v>
       </c>
       <c r="O8" s="66">
-        <v>0.00</v>
+        <v>172.00</v>
       </c>
       <c r="P8" s="65">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c t="inlineStr" r="Q8">
         <is>
@@ -658,26 +658,26 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">04/08/2026</t>
+          <t xml:space="preserve">03/08/2026</t>
         </is>
       </c>
       <c r="B9" s="65">
-        <v>70028</v>
+        <v>74872</v>
       </c>
       <c r="C9" s="66">
-        <v>130.00</v>
+        <v>120.00</v>
       </c>
       <c r="D9" s="66">
-        <v>300.00</v>
+        <v>310.00</v>
       </c>
       <c r="E9" s="66">
-        <v>69598.00</v>
+        <v>74442.00</v>
       </c>
       <c r="F9" s="66">
         <v>0.00</v>
       </c>
       <c r="G9" s="66">
-        <v>69598.00</v>
+        <v>74442.00</v>
       </c>
       <c r="H9" s="66">
         <v>0.00</v>
@@ -695,16 +695,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="66">
-        <v>69598.00</v>
+        <v>74442.00</v>
       </c>
       <c r="N9" s="66">
         <v>0.00</v>
       </c>
       <c r="O9" s="66">
-        <v>10.00</v>
+        <v>85.00</v>
       </c>
       <c r="P9" s="65">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c t="inlineStr" r="Q9">
         <is>
@@ -715,35 +715,35 @@
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">04/08/2026</t>
+          <t xml:space="preserve">03/08/2026</t>
         </is>
       </c>
       <c r="B10" s="65">
-        <v>24698</v>
+        <v>5941</v>
       </c>
       <c r="C10" s="66">
         <v>0.00</v>
       </c>
       <c r="D10" s="66">
-        <v>250.00</v>
+        <v>370.00</v>
       </c>
       <c r="E10" s="66">
-        <v>24448.00</v>
+        <v>5571.00</v>
       </c>
       <c r="F10" s="66">
         <v>0.00</v>
       </c>
       <c r="G10" s="66">
-        <v>24448.00</v>
+        <v>5571.00</v>
       </c>
       <c r="H10" s="66">
         <v>0.00</v>
       </c>
-      <c r="I10" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J10" s="66">
-        <v>0.00</v>
+      <c r="I10" s="65">
+        <v>0</v>
+      </c>
+      <c r="J10" s="65">
+        <v>0</v>
       </c>
       <c r="K10" s="65">
         <v>0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="M10" s="66">
-        <v>24448.00</v>
+        <v>5571.00</v>
       </c>
       <c r="N10" s="66">
         <v>0.00</v>
       </c>
       <c r="O10" s="66">
-        <v>169.00</v>
+        <v>0.00</v>
       </c>
       <c r="P10" s="65">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c t="inlineStr" r="Q10">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">05/08/2026</t>
+          <t xml:space="preserve">03/08/2026</t>
         </is>
       </c>
       <c r="B11" s="65">
-        <v>42706</v>
+        <v>20445</v>
       </c>
       <c r="C11" s="66">
-        <v>70.00</v>
+        <v>0.00</v>
       </c>
       <c r="D11" s="66">
-        <v>100.00</v>
+        <v>412.00</v>
       </c>
       <c r="E11" s="66">
-        <v>42536.00</v>
+        <v>20033.00</v>
       </c>
       <c r="F11" s="66">
         <v>0.00</v>
       </c>
       <c r="G11" s="66">
-        <v>42536.00</v>
+        <v>20033.00</v>
       </c>
       <c r="H11" s="66">
         <v>0.00</v>
       </c>
-      <c r="I11" s="65">
-        <v>0</v>
-      </c>
-      <c r="J11" s="65">
-        <v>0</v>
+      <c r="I11" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J11" s="66">
+        <v>0.00</v>
       </c>
       <c r="K11" s="65">
         <v>0</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="66">
-        <v>42536.00</v>
+        <v>20033.00</v>
       </c>
       <c r="N11" s="66">
         <v>0.00</v>
@@ -818,37 +818,37 @@
         <v>0.00</v>
       </c>
       <c r="P11" s="65">
-        <v>337</v>
+        <v>100</v>
       </c>
       <c t="inlineStr" r="Q11">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">05/08/2026</t>
+          <t xml:space="preserve">04/08/2026</t>
         </is>
       </c>
       <c r="B12" s="65">
-        <v>23594</v>
+        <v>70028</v>
       </c>
       <c r="C12" s="66">
-        <v>0.00</v>
+        <v>130.00</v>
       </c>
       <c r="D12" s="66">
-        <v>207.75</v>
+        <v>300.00</v>
       </c>
       <c r="E12" s="66">
-        <v>23386.25</v>
+        <v>69598.00</v>
       </c>
       <c r="F12" s="66">
         <v>0.00</v>
       </c>
       <c r="G12" s="66">
-        <v>23386.25</v>
+        <v>69598.00</v>
       </c>
       <c r="H12" s="66">
         <v>0.00</v>
@@ -866,55 +866,55 @@
         <v>0</v>
       </c>
       <c r="M12" s="66">
-        <v>23386.25</v>
+        <v>69598.00</v>
       </c>
       <c r="N12" s="66">
         <v>0.00</v>
       </c>
       <c r="O12" s="66">
-        <v>165.00</v>
+        <v>10.00</v>
       </c>
       <c r="P12" s="65">
-        <v>119</v>
+        <v>591</v>
       </c>
       <c t="inlineStr" r="Q12">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">06/08/2026</t>
+          <t xml:space="preserve">04/08/2026</t>
         </is>
       </c>
       <c r="B13" s="65">
-        <v>74405</v>
+        <v>4645</v>
       </c>
       <c r="C13" s="66">
-        <v>90.00</v>
-      </c>
-      <c r="D13" s="65">
-        <v>0</v>
+        <v>0.00</v>
+      </c>
+      <c r="D13" s="66">
+        <v>290.00</v>
       </c>
       <c r="E13" s="66">
-        <v>74315.00</v>
+        <v>4355.00</v>
       </c>
       <c r="F13" s="66">
         <v>0.00</v>
       </c>
       <c r="G13" s="66">
-        <v>74315.00</v>
+        <v>4355.00</v>
       </c>
       <c r="H13" s="66">
         <v>0.00</v>
       </c>
-      <c r="I13" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J13" s="66">
-        <v>0.00</v>
+      <c r="I13" s="65">
+        <v>0</v>
+      </c>
+      <c r="J13" s="65">
+        <v>0</v>
       </c>
       <c r="K13" s="65">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="66">
-        <v>74315.00</v>
+        <v>4355.00</v>
       </c>
       <c r="N13" s="66">
         <v>0.00</v>
@@ -932,37 +932,37 @@
         <v>0.00</v>
       </c>
       <c r="P13" s="65">
-        <v>616</v>
+        <v>22</v>
       </c>
       <c t="inlineStr" r="Q13">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">06/08/2026</t>
+          <t xml:space="preserve">04/08/2026</t>
         </is>
       </c>
       <c r="B14" s="65">
-        <v>22087</v>
+        <v>24698</v>
       </c>
       <c r="C14" s="66">
-        <v>71.70</v>
+        <v>0.00</v>
       </c>
       <c r="D14" s="66">
-        <v>282.50</v>
+        <v>250.00</v>
       </c>
       <c r="E14" s="66">
-        <v>21732.80</v>
+        <v>24448.00</v>
       </c>
       <c r="F14" s="66">
         <v>0.00</v>
       </c>
       <c r="G14" s="66">
-        <v>21732.80</v>
+        <v>24448.00</v>
       </c>
       <c r="H14" s="66">
         <v>0.00</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="66">
-        <v>21732.80</v>
+        <v>24448.00</v>
       </c>
       <c r="N14" s="66">
         <v>0.00</v>
       </c>
       <c r="O14" s="66">
-        <v>179.00</v>
+        <v>169.00</v>
       </c>
       <c r="P14" s="65">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c t="inlineStr" r="Q14">
         <is>
@@ -1000,26 +1000,26 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">07/08/2026</t>
+          <t xml:space="preserve">05/08/2026</t>
         </is>
       </c>
       <c r="B15" s="65">
-        <v>75949</v>
+        <v>23594</v>
       </c>
       <c r="C15" s="66">
-        <v>160.00</v>
+        <v>0.00</v>
       </c>
       <c r="D15" s="66">
-        <v>300.00</v>
+        <v>207.75</v>
       </c>
       <c r="E15" s="66">
-        <v>75489.00</v>
+        <v>23386.25</v>
       </c>
       <c r="F15" s="66">
         <v>0.00</v>
       </c>
       <c r="G15" s="66">
-        <v>75489.00</v>
+        <v>23386.25</v>
       </c>
       <c r="H15" s="66">
         <v>0.00</v>
@@ -1037,55 +1037,55 @@
         <v>0</v>
       </c>
       <c r="M15" s="66">
-        <v>75489.00</v>
+        <v>23386.25</v>
       </c>
       <c r="N15" s="66">
         <v>0.00</v>
       </c>
       <c r="O15" s="66">
-        <v>100.00</v>
+        <v>165.00</v>
       </c>
       <c r="P15" s="65">
-        <v>626</v>
+        <v>119</v>
       </c>
       <c t="inlineStr" r="Q15">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">07/08/2026</t>
+          <t xml:space="preserve">05/08/2026</t>
         </is>
       </c>
       <c r="B16" s="65">
-        <v>21195</v>
+        <v>42706</v>
       </c>
       <c r="C16" s="66">
-        <v>0.00</v>
+        <v>70.00</v>
       </c>
       <c r="D16" s="66">
-        <v>84.75</v>
+        <v>100.00</v>
       </c>
       <c r="E16" s="66">
-        <v>21110.25</v>
+        <v>42536.00</v>
       </c>
       <c r="F16" s="66">
         <v>0.00</v>
       </c>
       <c r="G16" s="66">
-        <v>21110.25</v>
+        <v>42536.00</v>
       </c>
       <c r="H16" s="66">
         <v>0.00</v>
       </c>
-      <c r="I16" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J16" s="66">
-        <v>0.00</v>
+      <c r="I16" s="65">
+        <v>0</v>
+      </c>
+      <c r="J16" s="65">
+        <v>0</v>
       </c>
       <c r="K16" s="65">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="66">
-        <v>21110.25</v>
+        <v>42536.00</v>
       </c>
       <c r="N16" s="66">
         <v>0.00</v>
@@ -1103,46 +1103,46 @@
         <v>0.00</v>
       </c>
       <c r="P16" s="65">
-        <v>101</v>
+        <v>337</v>
       </c>
       <c t="inlineStr" r="Q16">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">08/08/2026</t>
+          <t xml:space="preserve">05/08/2026</t>
         </is>
       </c>
       <c r="B17" s="65">
-        <v>52285</v>
+        <v>4619</v>
       </c>
       <c r="C17" s="66">
-        <v>200.00</v>
-      </c>
-      <c r="D17" s="65">
-        <v>0</v>
+        <v>0.00</v>
+      </c>
+      <c r="D17" s="66">
+        <v>194.75</v>
       </c>
       <c r="E17" s="66">
-        <v>52085.00</v>
+        <v>4424.25</v>
       </c>
       <c r="F17" s="66">
         <v>0.00</v>
       </c>
       <c r="G17" s="66">
-        <v>52085.00</v>
+        <v>4424.25</v>
       </c>
       <c r="H17" s="66">
         <v>0.00</v>
       </c>
-      <c r="I17" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J17" s="66">
-        <v>0.00</v>
+      <c r="I17" s="65">
+        <v>0</v>
+      </c>
+      <c r="J17" s="65">
+        <v>0</v>
       </c>
       <c r="K17" s="65">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="66">
-        <v>52085.00</v>
+        <v>4424.25</v>
       </c>
       <c r="N17" s="66">
         <v>0.00</v>
@@ -1160,37 +1160,37 @@
         <v>0.00</v>
       </c>
       <c r="P17" s="65">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c t="inlineStr" r="Q17">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">08/08/2026</t>
+          <t xml:space="preserve">06/08/2026</t>
         </is>
       </c>
       <c r="B18" s="65">
-        <v>23499</v>
+        <v>74405</v>
       </c>
       <c r="C18" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="D18" s="66">
-        <v>50.00</v>
+        <v>90.00</v>
+      </c>
+      <c r="D18" s="65">
+        <v>0</v>
       </c>
       <c r="E18" s="66">
-        <v>23449.00</v>
+        <v>74315.00</v>
       </c>
       <c r="F18" s="66">
         <v>0.00</v>
       </c>
       <c r="G18" s="66">
-        <v>23449.00</v>
+        <v>74315.00</v>
       </c>
       <c r="H18" s="66">
         <v>0.00</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="66">
-        <v>23449.00</v>
+        <v>74315.00</v>
       </c>
       <c r="N18" s="66">
         <v>0.00</v>
@@ -1217,46 +1217,46 @@
         <v>0.00</v>
       </c>
       <c r="P18" s="65">
-        <v>108</v>
+        <v>616</v>
       </c>
       <c t="inlineStr" r="Q18">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">09/08/2026</t>
+          <t xml:space="preserve">06/08/2026</t>
         </is>
       </c>
       <c r="B19" s="65">
-        <v>71001</v>
+        <v>6323</v>
       </c>
       <c r="C19" s="66">
         <v>0.00</v>
       </c>
       <c r="D19" s="66">
-        <v>200.00</v>
+        <v>292.50</v>
       </c>
       <c r="E19" s="66">
-        <v>70801.00</v>
+        <v>6030.50</v>
       </c>
       <c r="F19" s="66">
         <v>0.00</v>
       </c>
       <c r="G19" s="66">
-        <v>70801.00</v>
+        <v>6030.50</v>
       </c>
       <c r="H19" s="66">
         <v>0.00</v>
       </c>
-      <c r="I19" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J19" s="66">
-        <v>0.00</v>
+      <c r="I19" s="65">
+        <v>0</v>
+      </c>
+      <c r="J19" s="65">
+        <v>0</v>
       </c>
       <c r="K19" s="65">
         <v>0</v>
@@ -1265,46 +1265,46 @@
         <v>0</v>
       </c>
       <c r="M19" s="66">
-        <v>70801.00</v>
+        <v>6030.50</v>
       </c>
       <c r="N19" s="66">
         <v>0.00</v>
       </c>
       <c r="O19" s="66">
-        <v>120.00</v>
+        <v>0.00</v>
       </c>
       <c r="P19" s="65">
-        <v>597</v>
+        <v>32</v>
       </c>
       <c t="inlineStr" r="Q19">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">09/08/2026</t>
+          <t xml:space="preserve">06/08/2026</t>
         </is>
       </c>
       <c r="B20" s="65">
-        <v>27616</v>
+        <v>22087</v>
       </c>
       <c r="C20" s="66">
-        <v>0.00</v>
+        <v>71.70</v>
       </c>
       <c r="D20" s="66">
-        <v>210.00</v>
+        <v>282.50</v>
       </c>
       <c r="E20" s="66">
-        <v>27406.00</v>
+        <v>21732.80</v>
       </c>
       <c r="F20" s="66">
         <v>0.00</v>
       </c>
       <c r="G20" s="66">
-        <v>27406.00</v>
+        <v>21732.80</v>
       </c>
       <c r="H20" s="66">
         <v>0.00</v>
@@ -1322,16 +1322,16 @@
         <v>0</v>
       </c>
       <c r="M20" s="66">
-        <v>27406.00</v>
+        <v>21732.80</v>
       </c>
       <c r="N20" s="66">
         <v>0.00</v>
       </c>
       <c r="O20" s="66">
-        <v>0.00</v>
+        <v>179.00</v>
       </c>
       <c r="P20" s="65">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c t="inlineStr" r="Q20">
         <is>
@@ -1342,35 +1342,35 @@
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">10/08/2026</t>
+          <t xml:space="preserve">07/08/2026</t>
         </is>
       </c>
       <c r="B21" s="65">
-        <v>71003</v>
+        <v>75949</v>
       </c>
       <c r="C21" s="66">
-        <v>0.00</v>
+        <v>160.00</v>
       </c>
       <c r="D21" s="66">
         <v>300.00</v>
       </c>
       <c r="E21" s="66">
-        <v>70703.00</v>
+        <v>75489.00</v>
       </c>
       <c r="F21" s="66">
         <v>0.00</v>
       </c>
       <c r="G21" s="66">
-        <v>70703.00</v>
+        <v>75489.00</v>
       </c>
       <c r="H21" s="66">
         <v>0.00</v>
       </c>
-      <c r="I21" s="65">
-        <v>0</v>
-      </c>
-      <c r="J21" s="65">
-        <v>0</v>
+      <c r="I21" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J21" s="66">
+        <v>0.00</v>
       </c>
       <c r="K21" s="65">
         <v>0</v>
@@ -1379,16 +1379,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="66">
-        <v>70703.00</v>
+        <v>75489.00</v>
       </c>
       <c r="N21" s="66">
         <v>0.00</v>
       </c>
       <c r="O21" s="66">
-        <v>0.00</v>
+        <v>100.00</v>
       </c>
       <c r="P21" s="65">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c t="inlineStr" r="Q21">
         <is>
@@ -1399,35 +1399,35 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">10/08/2026</t>
+          <t xml:space="preserve">07/08/2026</t>
         </is>
       </c>
       <c r="B22" s="65">
-        <v>19148</v>
+        <v>4493</v>
       </c>
       <c r="C22" s="66">
         <v>0.00</v>
       </c>
       <c r="D22" s="66">
-        <v>222.50</v>
+        <v>84.75</v>
       </c>
       <c r="E22" s="66">
-        <v>18925.50</v>
+        <v>4408.25</v>
       </c>
       <c r="F22" s="66">
         <v>0.00</v>
       </c>
       <c r="G22" s="66">
-        <v>18925.50</v>
+        <v>4408.25</v>
       </c>
       <c r="H22" s="66">
         <v>0.00</v>
       </c>
-      <c r="I22" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J22" s="66">
-        <v>0.00</v>
+      <c r="I22" s="65">
+        <v>0</v>
+      </c>
+      <c r="J22" s="65">
+        <v>0</v>
       </c>
       <c r="K22" s="65">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="66">
-        <v>18925.50</v>
+        <v>4408.25</v>
       </c>
       <c r="N22" s="66">
         <v>0.00</v>
@@ -1445,46 +1445,46 @@
         <v>0.00</v>
       </c>
       <c r="P22" s="65">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c t="inlineStr" r="Q22">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">11/08/2026</t>
+          <t xml:space="preserve">07/08/2026</t>
         </is>
       </c>
       <c r="B23" s="65">
-        <v>72613</v>
+        <v>21195</v>
       </c>
       <c r="C23" s="66">
-        <v>110.00</v>
+        <v>0.00</v>
       </c>
       <c r="D23" s="66">
-        <v>100.00</v>
+        <v>84.75</v>
       </c>
       <c r="E23" s="66">
-        <v>72403.00</v>
+        <v>21110.25</v>
       </c>
       <c r="F23" s="66">
         <v>0.00</v>
       </c>
       <c r="G23" s="66">
-        <v>72403.00</v>
+        <v>21110.25</v>
       </c>
       <c r="H23" s="66">
         <v>0.00</v>
       </c>
-      <c r="I23" s="65">
-        <v>0</v>
-      </c>
-      <c r="J23" s="65">
-        <v>0</v>
+      <c r="I23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J23" s="66">
+        <v>0.00</v>
       </c>
       <c r="K23" s="65">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="66">
-        <v>72403.00</v>
+        <v>21110.25</v>
       </c>
       <c r="N23" s="66">
         <v>0.00</v>
@@ -1502,37 +1502,37 @@
         <v>0.00</v>
       </c>
       <c r="P23" s="65">
-        <v>632</v>
+        <v>101</v>
       </c>
       <c t="inlineStr" r="Q23">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">11/08/2026</t>
+          <t xml:space="preserve">08/08/2026</t>
         </is>
       </c>
       <c r="B24" s="65">
-        <v>22269</v>
+        <v>52285</v>
       </c>
       <c r="C24" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="D24" s="66">
-        <v>140.00</v>
+        <v>200.00</v>
+      </c>
+      <c r="D24" s="65">
+        <v>0</v>
       </c>
       <c r="E24" s="66">
-        <v>22129.00</v>
+        <v>52085.00</v>
       </c>
       <c r="F24" s="66">
         <v>0.00</v>
       </c>
       <c r="G24" s="66">
-        <v>22129.00</v>
+        <v>52085.00</v>
       </c>
       <c r="H24" s="66">
         <v>0.00</v>
@@ -1550,55 +1550,55 @@
         <v>0</v>
       </c>
       <c r="M24" s="66">
-        <v>22129.00</v>
+        <v>52085.00</v>
       </c>
       <c r="N24" s="66">
         <v>0.00</v>
       </c>
       <c r="O24" s="66">
-        <v>166.00</v>
+        <v>0.00</v>
       </c>
       <c r="P24" s="65">
-        <v>109</v>
+        <v>383</v>
       </c>
       <c t="inlineStr" r="Q24">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">12/08/2026</t>
+          <t xml:space="preserve">08/08/2026</t>
         </is>
       </c>
       <c r="B25" s="65">
-        <v>67035</v>
+        <v>5621</v>
       </c>
       <c r="C25" s="66">
-        <v>10.00</v>
-      </c>
-      <c r="D25" s="65">
-        <v>0</v>
+        <v>0.00</v>
+      </c>
+      <c r="D25" s="66">
+        <v>50.00</v>
       </c>
       <c r="E25" s="66">
-        <v>67025.00</v>
+        <v>5571.00</v>
       </c>
       <c r="F25" s="66">
         <v>0.00</v>
       </c>
       <c r="G25" s="66">
-        <v>67025.00</v>
+        <v>5571.00</v>
       </c>
       <c r="H25" s="66">
         <v>0.00</v>
       </c>
-      <c r="I25" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J25" s="66">
-        <v>0.00</v>
+      <c r="I25" s="65">
+        <v>0</v>
+      </c>
+      <c r="J25" s="65">
+        <v>0</v>
       </c>
       <c r="K25" s="65">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="66">
-        <v>67025.00</v>
+        <v>5571.00</v>
       </c>
       <c r="N25" s="66">
         <v>0.00</v>
@@ -1616,46 +1616,46 @@
         <v>0.00</v>
       </c>
       <c r="P25" s="65">
-        <v>568</v>
+        <v>25</v>
       </c>
       <c t="inlineStr" r="Q25">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">12/08/2026</t>
+          <t xml:space="preserve">08/08/2026</t>
         </is>
       </c>
       <c r="B26" s="65">
-        <v>23489</v>
+        <v>23499</v>
       </c>
       <c r="C26" s="66">
         <v>0.00</v>
       </c>
       <c r="D26" s="66">
-        <v>260.00</v>
+        <v>50.00</v>
       </c>
       <c r="E26" s="66">
-        <v>23229.00</v>
+        <v>23449.00</v>
       </c>
       <c r="F26" s="66">
         <v>0.00</v>
       </c>
       <c r="G26" s="66">
-        <v>23229.00</v>
+        <v>23449.00</v>
       </c>
       <c r="H26" s="66">
         <v>0.00</v>
       </c>
-      <c r="I26" s="65">
-        <v>0</v>
-      </c>
-      <c r="J26" s="65">
-        <v>0</v>
+      <c r="I26" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J26" s="66">
+        <v>0.00</v>
       </c>
       <c r="K26" s="65">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="66">
-        <v>23229.00</v>
+        <v>23449.00</v>
       </c>
       <c r="N26" s="66">
         <v>0.00</v>
@@ -1673,7 +1673,7 @@
         <v>0.00</v>
       </c>
       <c r="P26" s="65">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c t="inlineStr" r="Q26">
         <is>
@@ -1684,26 +1684,26 @@
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">13/08/2026</t>
+          <t xml:space="preserve">09/08/2026</t>
         </is>
       </c>
       <c r="B27" s="65">
-        <v>68394</v>
+        <v>27616</v>
       </c>
       <c r="C27" s="66">
-        <v>80.00</v>
+        <v>0.00</v>
       </c>
       <c r="D27" s="66">
-        <v>100.00</v>
+        <v>210.00</v>
       </c>
       <c r="E27" s="66">
-        <v>68214.00</v>
+        <v>27406.00</v>
       </c>
       <c r="F27" s="66">
         <v>0.00</v>
       </c>
       <c r="G27" s="66">
-        <v>68214.00</v>
+        <v>27406.00</v>
       </c>
       <c r="H27" s="66">
         <v>0.00</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="66">
-        <v>68214.00</v>
+        <v>27406.00</v>
       </c>
       <c r="N27" s="66">
         <v>0.00</v>
@@ -1730,37 +1730,37 @@
         <v>0.00</v>
       </c>
       <c r="P27" s="65">
-        <v>597</v>
+        <v>132</v>
       </c>
       <c t="inlineStr" r="Q27">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">13/08/2026</t>
+          <t xml:space="preserve">09/08/2026</t>
         </is>
       </c>
       <c r="B28" s="65">
-        <v>21290</v>
+        <v>7550</v>
       </c>
       <c r="C28" s="66">
         <v>0.00</v>
       </c>
       <c r="D28" s="66">
-        <v>90.00</v>
+        <v>210.00</v>
       </c>
       <c r="E28" s="66">
-        <v>21200.00</v>
+        <v>7340.00</v>
       </c>
       <c r="F28" s="66">
         <v>0.00</v>
       </c>
       <c r="G28" s="66">
-        <v>21200.00</v>
+        <v>7340.00</v>
       </c>
       <c r="H28" s="66">
         <v>0.00</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="66">
-        <v>21200.00</v>
+        <v>7340.00</v>
       </c>
       <c r="N28" s="66">
         <v>0.00</v>
@@ -1787,37 +1787,37 @@
         <v>0.00</v>
       </c>
       <c r="P28" s="65">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c t="inlineStr" r="Q28">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">14/08/2026</t>
+          <t xml:space="preserve">09/08/2026</t>
         </is>
       </c>
       <c r="B29" s="65">
-        <v>73510</v>
+        <v>71001</v>
       </c>
       <c r="C29" s="66">
-        <v>80.00</v>
+        <v>0.00</v>
       </c>
       <c r="D29" s="66">
-        <v>800.00</v>
+        <v>200.00</v>
       </c>
       <c r="E29" s="66">
-        <v>72630.00</v>
+        <v>70801.00</v>
       </c>
       <c r="F29" s="66">
         <v>0.00</v>
       </c>
       <c r="G29" s="66">
-        <v>72630.00</v>
+        <v>70801.00</v>
       </c>
       <c r="H29" s="66">
         <v>0.00</v>
@@ -1835,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="66">
-        <v>72630.00</v>
+        <v>70801.00</v>
       </c>
       <c r="N29" s="66">
         <v>0.00</v>
       </c>
       <c r="O29" s="66">
-        <v>0.00</v>
+        <v>120.00</v>
       </c>
       <c r="P29" s="65">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c t="inlineStr" r="Q29">
         <is>
@@ -1855,114 +1855,1425 @@
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
+          <t xml:space="preserve">10/08/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="65">
+        <v>71003</v>
+      </c>
+      <c r="C30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D30" s="66">
+        <v>300.00</v>
+      </c>
+      <c r="E30" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="F30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G30" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="H30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I30" s="65">
+        <v>0</v>
+      </c>
+      <c r="J30" s="65">
+        <v>0</v>
+      </c>
+      <c r="K30" s="65">
+        <v>0</v>
+      </c>
+      <c r="L30" s="65">
+        <v>0</v>
+      </c>
+      <c r="M30" s="66">
+        <v>70703.00</v>
+      </c>
+      <c r="N30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O30" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P30" s="65">
+        <v>602</v>
+      </c>
+      <c t="inlineStr" r="Q30">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c t="inlineStr" r="A31">
+        <is>
+          <t xml:space="preserve">10/08/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="65">
+        <v>5121</v>
+      </c>
+      <c r="C31" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D31" s="66">
+        <v>222.50</v>
+      </c>
+      <c r="E31" s="66">
+        <v>4898.50</v>
+      </c>
+      <c r="F31" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G31" s="66">
+        <v>4898.50</v>
+      </c>
+      <c r="H31" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I31" s="65">
+        <v>0</v>
+      </c>
+      <c r="J31" s="65">
+        <v>0</v>
+      </c>
+      <c r="K31" s="65">
+        <v>0</v>
+      </c>
+      <c r="L31" s="65">
+        <v>0</v>
+      </c>
+      <c r="M31" s="66">
+        <v>4898.50</v>
+      </c>
+      <c r="N31" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O31" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P31" s="65">
+        <v>28</v>
+      </c>
+      <c t="inlineStr" r="Q31">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c t="inlineStr" r="A32">
+        <is>
+          <t xml:space="preserve">10/08/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="65">
+        <v>19148</v>
+      </c>
+      <c r="C32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D32" s="66">
+        <v>222.50</v>
+      </c>
+      <c r="E32" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="F32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G32" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="H32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K32" s="65">
+        <v>0</v>
+      </c>
+      <c r="L32" s="65">
+        <v>0</v>
+      </c>
+      <c r="M32" s="66">
+        <v>18925.50</v>
+      </c>
+      <c r="N32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O32" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P32" s="65">
+        <v>103</v>
+      </c>
+      <c t="inlineStr" r="Q32">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c t="inlineStr" r="A33">
+        <is>
+          <t xml:space="preserve">11/08/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="65">
+        <v>72613</v>
+      </c>
+      <c r="C33" s="66">
+        <v>110.00</v>
+      </c>
+      <c r="D33" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E33" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="F33" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G33" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="H33" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I33" s="65">
+        <v>0</v>
+      </c>
+      <c r="J33" s="65">
+        <v>0</v>
+      </c>
+      <c r="K33" s="65">
+        <v>0</v>
+      </c>
+      <c r="L33" s="65">
+        <v>0</v>
+      </c>
+      <c r="M33" s="66">
+        <v>72403.00</v>
+      </c>
+      <c r="N33" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O33" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P33" s="65">
+        <v>632</v>
+      </c>
+      <c t="inlineStr" r="Q33">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c t="inlineStr" r="A34">
+        <is>
+          <t xml:space="preserve">11/08/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="65">
+        <v>5271</v>
+      </c>
+      <c r="C34" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D34" s="66">
+        <v>140.00</v>
+      </c>
+      <c r="E34" s="66">
+        <v>5131.00</v>
+      </c>
+      <c r="F34" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G34" s="66">
+        <v>5131.00</v>
+      </c>
+      <c r="H34" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I34" s="65">
+        <v>0</v>
+      </c>
+      <c r="J34" s="65">
+        <v>0</v>
+      </c>
+      <c r="K34" s="65">
+        <v>0</v>
+      </c>
+      <c r="L34" s="65">
+        <v>0</v>
+      </c>
+      <c r="M34" s="66">
+        <v>5131.00</v>
+      </c>
+      <c r="N34" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O34" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P34" s="65">
+        <v>28</v>
+      </c>
+      <c t="inlineStr" r="Q34">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c t="inlineStr" r="A35">
+        <is>
+          <t xml:space="preserve">11/08/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="65">
+        <v>22269</v>
+      </c>
+      <c r="C35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D35" s="66">
+        <v>140.00</v>
+      </c>
+      <c r="E35" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="F35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G35" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="H35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K35" s="65">
+        <v>0</v>
+      </c>
+      <c r="L35" s="65">
+        <v>0</v>
+      </c>
+      <c r="M35" s="66">
+        <v>22129.00</v>
+      </c>
+      <c r="N35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O35" s="66">
+        <v>166.00</v>
+      </c>
+      <c r="P35" s="65">
+        <v>109</v>
+      </c>
+      <c t="inlineStr" r="Q35">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c t="inlineStr" r="A36">
+        <is>
+          <t xml:space="preserve">12/08/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="65">
+        <v>67035</v>
+      </c>
+      <c r="C36" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="D36" s="65">
+        <v>0</v>
+      </c>
+      <c r="E36" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="F36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G36" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="H36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K36" s="65">
+        <v>0</v>
+      </c>
+      <c r="L36" s="65">
+        <v>0</v>
+      </c>
+      <c r="M36" s="66">
+        <v>67025.00</v>
+      </c>
+      <c r="N36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O36" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P36" s="65">
+        <v>568</v>
+      </c>
+      <c t="inlineStr" r="Q36">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c t="inlineStr" r="A37">
+        <is>
+          <t xml:space="preserve">12/08/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="65">
+        <v>7766</v>
+      </c>
+      <c r="C37" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D37" s="66">
+        <v>260.00</v>
+      </c>
+      <c r="E37" s="66">
+        <v>7506.00</v>
+      </c>
+      <c r="F37" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G37" s="66">
+        <v>7506.00</v>
+      </c>
+      <c r="H37" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I37" s="65">
+        <v>0</v>
+      </c>
+      <c r="J37" s="65">
+        <v>0</v>
+      </c>
+      <c r="K37" s="65">
+        <v>0</v>
+      </c>
+      <c r="L37" s="65">
+        <v>0</v>
+      </c>
+      <c r="M37" s="66">
+        <v>7506.00</v>
+      </c>
+      <c r="N37" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O37" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P37" s="65">
+        <v>35</v>
+      </c>
+      <c t="inlineStr" r="Q37">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c t="inlineStr" r="A38">
+        <is>
+          <t xml:space="preserve">12/08/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="65">
+        <v>23489</v>
+      </c>
+      <c r="C38" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D38" s="66">
+        <v>260.00</v>
+      </c>
+      <c r="E38" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="F38" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G38" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="H38" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I38" s="65">
+        <v>0</v>
+      </c>
+      <c r="J38" s="65">
+        <v>0</v>
+      </c>
+      <c r="K38" s="65">
+        <v>0</v>
+      </c>
+      <c r="L38" s="65">
+        <v>0</v>
+      </c>
+      <c r="M38" s="66">
+        <v>23229.00</v>
+      </c>
+      <c r="N38" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O38" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P38" s="65">
+        <v>111</v>
+      </c>
+      <c t="inlineStr" r="Q38">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c t="inlineStr" r="A39">
+        <is>
+          <t xml:space="preserve">13/08/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="65">
+        <v>21290</v>
+      </c>
+      <c r="C39" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D39" s="66">
+        <v>90.00</v>
+      </c>
+      <c r="E39" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="F39" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G39" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="H39" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I39" s="65">
+        <v>0</v>
+      </c>
+      <c r="J39" s="65">
+        <v>0</v>
+      </c>
+      <c r="K39" s="65">
+        <v>0</v>
+      </c>
+      <c r="L39" s="65">
+        <v>0</v>
+      </c>
+      <c r="M39" s="66">
+        <v>21200.00</v>
+      </c>
+      <c r="N39" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O39" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P39" s="65">
+        <v>93</v>
+      </c>
+      <c t="inlineStr" r="Q39">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c t="inlineStr" r="A40">
+        <is>
+          <t xml:space="preserve">13/08/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="65">
+        <v>6688</v>
+      </c>
+      <c r="C40" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D40" s="66">
+        <v>90.00</v>
+      </c>
+      <c r="E40" s="66">
+        <v>6598.00</v>
+      </c>
+      <c r="F40" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G40" s="66">
+        <v>6598.00</v>
+      </c>
+      <c r="H40" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I40" s="65">
+        <v>0</v>
+      </c>
+      <c r="J40" s="65">
+        <v>0</v>
+      </c>
+      <c r="K40" s="65">
+        <v>0</v>
+      </c>
+      <c r="L40" s="65">
+        <v>0</v>
+      </c>
+      <c r="M40" s="66">
+        <v>6598.00</v>
+      </c>
+      <c r="N40" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O40" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P40" s="65">
+        <v>33</v>
+      </c>
+      <c t="inlineStr" r="Q40">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c t="inlineStr" r="A41">
+        <is>
+          <t xml:space="preserve">13/08/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="65">
+        <v>68394</v>
+      </c>
+      <c r="C41" s="66">
+        <v>80.00</v>
+      </c>
+      <c r="D41" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E41" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="F41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G41" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="H41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K41" s="65">
+        <v>0</v>
+      </c>
+      <c r="L41" s="65">
+        <v>0</v>
+      </c>
+      <c r="M41" s="66">
+        <v>68214.00</v>
+      </c>
+      <c r="N41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P41" s="65">
+        <v>597</v>
+      </c>
+      <c t="inlineStr" r="Q41">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c t="inlineStr" r="A42">
+        <is>
           <t xml:space="preserve">14/08/2026</t>
         </is>
       </c>
-      <c r="B30" s="65">
+      <c r="B42" s="65">
+        <v>73510</v>
+      </c>
+      <c r="C42" s="66">
+        <v>80.00</v>
+      </c>
+      <c r="D42" s="66">
+        <v>800.00</v>
+      </c>
+      <c r="E42" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="F42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G42" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="H42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K42" s="65">
+        <v>0</v>
+      </c>
+      <c r="L42" s="65">
+        <v>0</v>
+      </c>
+      <c r="M42" s="66">
+        <v>72630.00</v>
+      </c>
+      <c r="N42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O42" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P42" s="65">
+        <v>570</v>
+      </c>
+      <c t="inlineStr" r="Q42">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c t="inlineStr" r="A43">
+        <is>
+          <t xml:space="preserve">14/08/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="65">
+        <v>5649</v>
+      </c>
+      <c r="C43" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D43" s="66">
+        <v>187.50</v>
+      </c>
+      <c r="E43" s="66">
+        <v>5461.50</v>
+      </c>
+      <c r="F43" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G43" s="66">
+        <v>5461.50</v>
+      </c>
+      <c r="H43" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I43" s="65">
+        <v>0</v>
+      </c>
+      <c r="J43" s="65">
+        <v>0</v>
+      </c>
+      <c r="K43" s="65">
+        <v>0</v>
+      </c>
+      <c r="L43" s="65">
+        <v>0</v>
+      </c>
+      <c r="M43" s="66">
+        <v>5461.50</v>
+      </c>
+      <c r="N43" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O43" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P43" s="65">
+        <v>28</v>
+      </c>
+      <c t="inlineStr" r="Q43">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c t="inlineStr" r="A44">
+        <is>
+          <t xml:space="preserve">14/08/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="65">
         <v>17640</v>
       </c>
-      <c r="C30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="D30" s="66">
+      <c r="C44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D44" s="66">
         <v>187.50</v>
       </c>
-      <c r="E30" s="66">
+      <c r="E44" s="66">
         <v>17452.50</v>
       </c>
-      <c r="F30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="G30" s="66">
+      <c r="F44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G44" s="66">
         <v>17452.50</v>
       </c>
-      <c r="H30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="I30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="K30" s="65">
-        <v>0</v>
-      </c>
-      <c r="L30" s="65">
-        <v>0</v>
-      </c>
-      <c r="M30" s="66">
+      <c r="H44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K44" s="65">
+        <v>0</v>
+      </c>
+      <c r="L44" s="65">
+        <v>0</v>
+      </c>
+      <c r="M44" s="66">
         <v>17452.50</v>
       </c>
-      <c r="N30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="O30" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="P30" s="65">
+      <c r="N44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O44" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P44" s="65">
         <v>93</v>
       </c>
-      <c t="inlineStr" r="Q30">
+      <c t="inlineStr" r="Q44">
         <is>
           <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c t="inlineStr" r="A31" s="2">
+    <row r="45">
+      <c t="inlineStr" r="A45">
+        <is>
+          <t xml:space="preserve">15/08/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="65">
+        <v>73249</v>
+      </c>
+      <c r="C45" s="66">
+        <v>70.00</v>
+      </c>
+      <c r="D45" s="66">
+        <v>500.00</v>
+      </c>
+      <c r="E45" s="66">
+        <v>72679.00</v>
+      </c>
+      <c r="F45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G45" s="66">
+        <v>72679.00</v>
+      </c>
+      <c r="H45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K45" s="65">
+        <v>0</v>
+      </c>
+      <c r="L45" s="65">
+        <v>0</v>
+      </c>
+      <c r="M45" s="66">
+        <v>72679.00</v>
+      </c>
+      <c r="N45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O45" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P45" s="65">
+        <v>600</v>
+      </c>
+      <c t="inlineStr" r="Q45">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c t="inlineStr" r="A46">
+        <is>
+          <t xml:space="preserve">15/08/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="65">
+        <v>7813</v>
+      </c>
+      <c r="C46" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D46" s="66">
+        <v>324.75</v>
+      </c>
+      <c r="E46" s="66">
+        <v>7488.25</v>
+      </c>
+      <c r="F46" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G46" s="66">
+        <v>7488.25</v>
+      </c>
+      <c r="H46" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I46" s="65">
+        <v>0</v>
+      </c>
+      <c r="J46" s="65">
+        <v>0</v>
+      </c>
+      <c r="K46" s="65">
+        <v>0</v>
+      </c>
+      <c r="L46" s="65">
+        <v>0</v>
+      </c>
+      <c r="M46" s="66">
+        <v>7488.25</v>
+      </c>
+      <c r="N46" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O46" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P46" s="65">
+        <v>37</v>
+      </c>
+      <c t="inlineStr" r="Q46">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c t="inlineStr" r="A47">
+        <is>
+          <t xml:space="preserve">15/08/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="65">
+        <v>24089</v>
+      </c>
+      <c r="C47" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D47" s="66">
+        <v>324.75</v>
+      </c>
+      <c r="E47" s="66">
+        <v>23764.25</v>
+      </c>
+      <c r="F47" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G47" s="66">
+        <v>23764.25</v>
+      </c>
+      <c r="H47" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I47" s="65">
+        <v>0</v>
+      </c>
+      <c r="J47" s="65">
+        <v>0</v>
+      </c>
+      <c r="K47" s="65">
+        <v>0</v>
+      </c>
+      <c r="L47" s="65">
+        <v>0</v>
+      </c>
+      <c r="M47" s="66">
+        <v>23764.25</v>
+      </c>
+      <c r="N47" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O47" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P47" s="65">
+        <v>120</v>
+      </c>
+      <c t="inlineStr" r="Q47">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c t="inlineStr" r="A48">
+        <is>
+          <t xml:space="preserve">16/08/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="65">
+        <v>76749</v>
+      </c>
+      <c r="C48" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="D48" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E48" s="66">
+        <v>76639.00</v>
+      </c>
+      <c r="F48" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G48" s="66">
+        <v>76639.00</v>
+      </c>
+      <c r="H48" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I48" s="65">
+        <v>0</v>
+      </c>
+      <c r="J48" s="65">
+        <v>0</v>
+      </c>
+      <c r="K48" s="65">
+        <v>0</v>
+      </c>
+      <c r="L48" s="65">
+        <v>0</v>
+      </c>
+      <c r="M48" s="66">
+        <v>76639.00</v>
+      </c>
+      <c r="N48" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O48" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P48" s="65">
+        <v>624</v>
+      </c>
+      <c t="inlineStr" r="Q48">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c t="inlineStr" r="A49">
+        <is>
+          <t xml:space="preserve">16/08/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="65">
+        <v>7109</v>
+      </c>
+      <c r="C49" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D49" s="66">
+        <v>125.00</v>
+      </c>
+      <c r="E49" s="66">
+        <v>6984.00</v>
+      </c>
+      <c r="F49" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G49" s="66">
+        <v>6984.00</v>
+      </c>
+      <c r="H49" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I49" s="65">
+        <v>0</v>
+      </c>
+      <c r="J49" s="65">
+        <v>0</v>
+      </c>
+      <c r="K49" s="65">
+        <v>0</v>
+      </c>
+      <c r="L49" s="65">
+        <v>0</v>
+      </c>
+      <c r="M49" s="66">
+        <v>6984.00</v>
+      </c>
+      <c r="N49" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O49" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P49" s="65">
+        <v>30</v>
+      </c>
+      <c t="inlineStr" r="Q49">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c t="inlineStr" r="A50">
+        <is>
+          <t xml:space="preserve">16/08/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="65">
+        <v>23867</v>
+      </c>
+      <c r="C50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D50" s="66">
+        <v>125.00</v>
+      </c>
+      <c r="E50" s="66">
+        <v>23742.00</v>
+      </c>
+      <c r="F50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G50" s="66">
+        <v>23742.00</v>
+      </c>
+      <c r="H50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K50" s="65">
+        <v>0</v>
+      </c>
+      <c r="L50" s="65">
+        <v>0</v>
+      </c>
+      <c r="M50" s="66">
+        <v>23742.00</v>
+      </c>
+      <c r="N50" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O50" s="66">
+        <v>393.00</v>
+      </c>
+      <c r="P50" s="65">
+        <v>105</v>
+      </c>
+      <c t="inlineStr" r="Q50">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c t="inlineStr" r="A51">
+        <is>
+          <t xml:space="preserve">17/08/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="65">
+        <v>64960</v>
+      </c>
+      <c r="C51" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="D51" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E51" s="66">
+        <v>64840.00</v>
+      </c>
+      <c r="F51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G51" s="66">
+        <v>64840.00</v>
+      </c>
+      <c r="H51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K51" s="65">
+        <v>0</v>
+      </c>
+      <c r="L51" s="65">
+        <v>0</v>
+      </c>
+      <c r="M51" s="66">
+        <v>64840.00</v>
+      </c>
+      <c r="N51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O51" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P51" s="65">
+        <v>578</v>
+      </c>
+      <c t="inlineStr" r="Q51">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c t="inlineStr" r="A52">
+        <is>
+          <t xml:space="preserve">17/08/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="65">
+        <v>5668</v>
+      </c>
+      <c r="C52" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D52" s="66">
+        <v>142.50</v>
+      </c>
+      <c r="E52" s="66">
+        <v>5525.50</v>
+      </c>
+      <c r="F52" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G52" s="66">
+        <v>5525.50</v>
+      </c>
+      <c r="H52" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I52" s="65">
+        <v>0</v>
+      </c>
+      <c r="J52" s="65">
+        <v>0</v>
+      </c>
+      <c r="K52" s="65">
+        <v>0</v>
+      </c>
+      <c r="L52" s="65">
+        <v>0</v>
+      </c>
+      <c r="M52" s="66">
+        <v>5525.50</v>
+      </c>
+      <c r="N52" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O52" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P52" s="65">
+        <v>21</v>
+      </c>
+      <c t="inlineStr" r="Q52">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c t="inlineStr" r="A53">
+        <is>
+          <t xml:space="preserve">17/08/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="65">
+        <v>19154</v>
+      </c>
+      <c r="C53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D53" s="66">
+        <v>142.50</v>
+      </c>
+      <c r="E53" s="66">
+        <v>19011.50</v>
+      </c>
+      <c r="F53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G53" s="66">
+        <v>19011.50</v>
+      </c>
+      <c r="H53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K53" s="65">
+        <v>0</v>
+      </c>
+      <c r="L53" s="65">
+        <v>0</v>
+      </c>
+      <c r="M53" s="66">
+        <v>19011.50</v>
+      </c>
+      <c r="N53" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O53" s="66">
+        <v>120.00</v>
+      </c>
+      <c r="P53" s="65">
+        <v>85</v>
+      </c>
+      <c t="inlineStr" r="Q53">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c t="inlineStr" r="A54" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B31" s="2">
-        <v>1295603.00</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1491.70</v>
-      </c>
-      <c r="D31" s="2">
-        <v>6639.50</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="K31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="M31" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="N31" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="O31" s="2">
-        <v>1541.00</v>
-      </c>
-      <c r="P31" s="2">
-        <v>9655.00</v>
+      <c r="B54" s="2">
+        <v>1677029.00</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1591.70</v>
+      </c>
+      <c r="D54" s="2">
+        <v>11298.50</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="O54" s="2">
+        <v>2054.00</v>
+      </c>
+      <c r="P54" s="2">
+        <v>12233.00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q30"/>
+  <autoFilter ref="A2:Q53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
